--- a/human_validation/judge/kor/judge_D008_S001_P003__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D008_S001_P003__qwen3-235b_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B76"/>
+  <dimension ref="A1:B68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,376 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 진료실에 오신 것을 환영합니다. 저는 [이름] 선생님입니다. 오늘 어떤 일로 오시게 되었는지 말씀해 주시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 네, 요즘 머리가 좀 멍한 느낌이 들어서 왔어요. 직장에서 고객 기록에 작은 실수들을 하고, 방금 뭘 하려던 건지 잊어버리기도 해요. 원래 저는 그런 사람이 아닌데, 그래서 한번 확인받아야겠다고 생각했어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 멍한 느낌이 들 때 정확히 어떤 일이 일어나는지 설명해 주시겠어요? 예를 들어 최근 있었던 일을 기억하는 게 힘드시거나, 대화를 따라가기 어렵거나, 자신이 어디 있는지 헷갈리시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 주로 생각의 흐름을 놓치는 느낌이에요. 뭘 하려다가 그게 뭐였는지 잊어버리거나, 고객 기록을 쓰다가 평소라면 안 했을 작은 실수를 했다는 걸 나중에 알아차려요. 제가 어디 있는지 모른다거나 그런 건 아니고요—그냥 머릿속이 멍하고 느려진 느낌에 가까워요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 기분이 가라앉거나 절망감을 느끼시거나, 평소에 즐기시던 일들에 흥미를 잃으신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 네... 요즘 꽤 기분이 가라앉아 있어요. 거의 매일 아침 가슴에 무겁고 텅 빈 느낌을 안고 일어나요. 근무는 그럭저럭 버티고 사람들이랑 얘기도 하긴 하는데, 속으로는 그냥 슬프고 멍한 느낌이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 이 멍한 느낌이 특별히 불안하거나 스트레스를 받을 때 더 나타나는 것 같으세요, 아니면 그냥 기분이 가라앉아 있을 때 더 많이 나타나는 것 같으세요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 기분이 가라앉아 있을 때 더 많이 나타나는 것 같아요. 불안하거나 스트레스받아서 그런 건 별로 못 느꼈어요. 그냥 머리가 멍해지고, 그러다 기록에 작은 실수를 하거나 뭘 하려던 건지 잊어버리게 돼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 지난 몇 달 동안 명확하게 생각하거나 기억하는 능력이 더 나빠지고 있다고 느끼세요, 아니면 평소 기분이 가라앉을 때 느끼는 정도와 비슷한 수준인가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 네, 요즘 더 두드러지는 것 같아요. 기분이 가라앉을 때 머리가 그냥 멍해지고, 뭘 하려던 건지 잊어버리거나 고객 기록에서 작은 실수를 발견하게 돼요. 원래 제가 그런 사람이 아니라서, 그게 제가 오게 된 이유 중 하나예요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 취미나 일, 친구나 가족과 보내는 시간처럼 예전에 즐기시던 활동들에 흥미나 즐거움이 줄어든 걸 느끼셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 잘 모르겠어요. 모든 것에 관심이 없어졌다고는 못 하겠지만, 요즘 뭘 해도 예전만큼 즐겁지가 않아요. 해야 할 건 여전히 하는데, 거기서 얻는 게 별로 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 정서적으로나 정신적으로 느끼시는 상태 때문에 침대에서 일어나거나 기본적인 일을 처리하는 것조차 힘들었던 날이 있으셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 보통 침대에서 못 일어날 정도까지는 아니에요. 근데 세세한 부분에서 예전만큼 믿을 만하지 못해졌어요. 직장에서는 동료들한테 고객 서류를 다시 확인해달라고 부탁해야 했고, 집에서는 제가 평소보다 뭘 많이 놓치니까 아내가 청구서나 일정 관리 일부를 대신 맡고 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 집중이나 기억에 있어서의 어려움이 예전보다 확연히 더 심해져서, 직장 업무나 평소의 책임을 수행하는 데 분명히 지장을 줄 정도라고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 네, 어느 정도 지장을 주고 있는 것 같아요. 직장에서는 세부 내용에 대한 제 자신을 못 믿어서 동료들한테 고객 기록을 다시 확인해달라고 부탁하고 있고요. 집에서도 제가 평소보다 많이 놓치다 보니 아내가 청구서나 일정 관리 일부를 맡게 됐어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사 질문] 정서적으로 이런 상태이고 멍한 사고와 건망증을 겪으신 게 얼마나 되셨나요? 적어도 2주 이상 지속되고 있나요, 아니면 시간이 지나면서 왔다 갔다 했나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 환자 응답] 적어도 몇 주 동안은 계속됐어요. 가라앉은 기분이랑 죄책감, 그리고 멍한 사고가 한 달 정도 저를 계속 짓누르고 있는 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사 질문] 기분이 가라앉거나 정서적으로 저조하지 않을 때도 기억이나 사고에 문제가 생기는 걸 느끼셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 환자 응답] 주로 기분이 가라앉아 있을 때 나타나는 것 같아요. 그럴 때 머리가 멍해지고, 고객 기록에 작은 실수를 하거나 뭘 하려던 건지 잊어버려요. 기분이 괜찮을 때는 그런 일이 똑같이 일어나는 걸 별로 못 느꼈어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사 질문] 요즘 평소보다 죄책감을 느끼거나 스스로를 탓하는 일이 많아지셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 환자 응답] 네. 요즘 스스로를 많이 탓하게 돼요, 특히 저희 삼촌 일로요. 좀 더 자주 전화드리거나 돌아가시기 전에 좀 더 일찍 찾아뵀어야 했는데 하는 생각이 계속 들어요. 머릿속에서 계속 반복 재생되는데, 가족으로서 삼촌한테 못 한 것 같은 느낌이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사 질문] 예전에 기분이 비교적 괜찮았던 시기에도 기억이나 집중력에 문제가 있었던 걸 느끼신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 환자 응답] 아니요, 딱히 없었어요. 기분이 괜찮았을 때는 이런 멍한 느낌이 있었던 기억이 없어요. 지금 제가 온 이유는 머리가 흐릿한 느낌이 들고, 고객 기록에 작은 실수를 하거나 뭘 하려던 건지 잊어버리는데, 이게 저한테는 정상이 아니라서예요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사 질문] 지금까지 보면 기억이나 집중력 문제가 기분이 가라앉아 있을 때만 나타나나요, 아니면 기분이 괜찮았는데도 그런 문제가 있었던 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 환자 응답] 기분이 가라앉아 있을 때만 그런 것 같아요. 그럴 때 머리가 멍해지고, 고객 기록에 작은 실수를 하기 시작하거나 뭘 하려던 건지 잊어버려요. 기분이 괜찮을 때는 딱히 못 느껴요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사 질문] 즐겨 보던 프로그램을 보거나, 친구들과 시간을 보내거나, 취미 활동을 하는 것처럼 예전에 즐기시던 대부분의 활동에서 즐거움이나 흥미를 못 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 환자 응답] 그렇게까지는 말 못 하겠어요. 가끔은 여전히 뭔가를 즐길 수 있는데, 대부분의 것들에 흥미가 있는지 없는지는 딱히 신경 써서 살펴보진 않았어요. 그보다는... 어떤 날은 그냥 뭘 할 기분이 안 나는 정도예요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사 질문] 예전에 가장 즐기시던 것들을 포함해서 거의 모든 활동에 흥미를 잃으시거나 즐거움을 거의 못 느끼셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 환자 응답] 거의 모든 활동이라고 할 수 있을지는 잘 모르겠어요. 뭘 하고 싶지 않은 시기는 있었지만, 평소에 즐기던 모든 것에 완전히 흥미를 잃었다고는 못 하겠어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사 질문] 적어도 2주 연속으로, 거의 매일 하루의 대부분 동안 기분이 가라앉거나 흥미를 잃은 날들이 있으셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 환자 응답] 네... 요즘 가슴에 무겁고 좀 텅 빈 느낌을 안고 일어나요. 근무는 그럭저럭 버티고 사람들이랑 얘기도 하는데, 속으로는 하루의 많은 시간 동안 그냥 슬프고 멍한 느낌이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사 질문] 정말 좋아하시던 것들을 포함해서 거의 모든 활동에 흥미를 잃거나 즐거움을 전혀 못 느끼셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 환자 응답] 거의 모든 활동이라고는 못 하겠어요. 가끔 의욕이 줄어든 건 느끼는데, 그래도 여전히 이따금 뭔가에서 즐거움을 느낄 수는 있어요. 모든 게 완전히 무의미하거나 공허하게 느껴지는 건 아니에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
         <is>
           <t>진단명: 제1형 양극성장애 (D008)
 인구통계: 성별 남성 / 나이 43 / 직업상태 personal care aide / 최종학력 대학 재학
@@ -575,434 +936,46 @@
 증상 지속 기간: None
 추가 요건: 
 주호소 증상 코드: S031
-배경 서술: 구스타보를 키우는 데 큰 도움을 주었던, 시우다드후아레스에 사는 사랑하는 삼촌이 세상을 떠난 뒤, 그는 끊임없이 바쁘게 움직이면 상실감을 억누를 수 있다는 듯이 가족 일 처리, 장례 준비, 차량 수리, 그리고 자신의 간호조무사(CNA) 진로 계획에 몰두했다. 이후 2주 동안 그는 잠을 거의 자지 않아도 괜찮았고, 스페인어 사용 노인 돌봄 기관을 당장 시작할 수 있다는 유난한 자신감을 보였으며, 주의가 산만해져 고객 관련 서류 작업에서 실수를 저지르기도 했지만, 아내와 동료들이 대부분의 문제를 초기에 알아챘다. 그다음 2주 동안 그는 삼촌을 위해 더 많은 것을 하지 못했다는 죄책감과 함께 지속적으로 기분이 가라앉고 피로했으며, 집중력 저하, 불규칙한 수면, 그리고 그를 불안하게 만드는 수동적인 죽음에 대한 생각을 겪었다. 그는 주치의와의 정기 진료 중 이를 언급했고, 주치의는 조울증 양상을 알아채고 그를 이중언어가 가능한 외래 정신건강의학과 전문의에게 의뢰했다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 진료실에 오신 것을 환영합니다. 저는 [이름] 선생님입니다. 오늘 어떤 일로 오시게 되었는지 말씀해 주시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 네, 요즘 머리가 좀 멍한 느낌이 들어서 왔어요. 직장에서 고객 기록에 작은 실수들을 하고, 방금 뭘 하려던 건지 잊어버리기도 해요. 원래 저는 그런 사람이 아닌데, 그래서 한번 확인받아야겠다고 생각했어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 멍한 느낌이 들 때 정확히 어떤 일이 일어나는지 설명해 주시겠어요? 예를 들어 최근 있었던 일을 기억하는 게 힘드시거나, 대화를 따라가기 어렵거나, 자신이 어디 있는지 헷갈리시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 주로 생각의 흐름을 놓치는 느낌이에요. 뭘 하려다가 그게 뭐였는지 잊어버리거나, 고객 기록을 쓰다가 평소라면 안 했을 작은 실수를 했다는 걸 나중에 알아차려요. 제가 어디 있는지 모른다거나 그런 건 아니고요—그냥 머릿속이 멍하고 느려진 느낌에 가까워요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 기분이 가라앉거나 절망감을 느끼시거나, 평소에 즐기시던 일들에 흥미를 잃으신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 네... 요즘 꽤 기분이 가라앉아 있어요. 거의 매일 아침 가슴에 무겁고 텅 빈 느낌을 안고 일어나요. 근무는 그럭저럭 버티고 사람들이랑 얘기도 하긴 하는데, 속으로는 그냥 슬프고 멍한 느낌이에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 이 멍한 느낌이 특별히 불안하거나 스트레스를 받을 때 더 나타나는 것 같으세요, 아니면 그냥 기분이 가라앉아 있을 때 더 많이 나타나는 것 같으세요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 기분이 가라앉아 있을 때 더 많이 나타나는 것 같아요. 불안하거나 스트레스받아서 그런 건 별로 못 느꼈어요. 그냥 머리가 멍해지고, 그러다 기록에 작은 실수를 하거나 뭘 하려던 건지 잊어버리게 돼요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 지난 몇 달 동안 명확하게 생각하거나 기억하는 능력이 더 나빠지고 있다고 느끼세요, 아니면 평소 기분이 가라앉을 때 느끼는 정도와 비슷한 수준인가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 네, 요즘 더 두드러지는 것 같아요. 기분이 가라앉을 때 머리가 그냥 멍해지고, 뭘 하려던 건지 잊어버리거나 고객 기록에서 작은 실수를 발견하게 돼요. 원래 제가 그런 사람이 아니라서, 그게 제가 오게 된 이유 중 하나예요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 취미나 일, 친구나 가족과 보내는 시간처럼 예전에 즐기시던 활동들에 흥미나 즐거움이 줄어든 걸 느끼셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 잘 모르겠어요. 모든 것에 관심이 없어졌다고는 못 하겠지만, 요즘 뭘 해도 예전만큼 즐겁지가 않아요. 해야 할 건 여전히 하는데, 거기서 얻는 게 별로 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 정서적으로나 정신적으로 느끼시는 상태 때문에 침대에서 일어나거나 기본적인 일을 처리하는 것조차 힘들었던 날이 있으셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 보통 침대에서 못 일어날 정도까지는 아니에요. 근데 세세한 부분에서 예전만큼 믿을 만하지 못해졌어요. 직장에서는 동료들한테 고객 서류를 다시 확인해달라고 부탁해야 했고, 집에서는 제가 평소보다 뭘 많이 놓치니까 아내가 청구서나 일정 관리 일부를 대신 맡고 있어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 집중이나 기억에 있어서의 어려움이 예전보다 확연히 더 심해져서, 직장 업무나 평소의 책임을 수행하는 데 분명히 지장을 줄 정도라고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 네, 어느 정도 지장을 주고 있는 것 같아요. 직장에서는 세부 내용에 대한 제 자신을 못 믿어서 동료들한테 고객 기록을 다시 확인해달라고 부탁하고 있고요. 집에서도 제가 평소보다 많이 놓치다 보니 아내가 청구서나 일정 관리 일부를 맡게 됐어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사 질문] 정서적으로 이런 상태이고 멍한 사고와 건망증을 겪으신 게 얼마나 되셨나요? 적어도 2주 이상 지속되고 있나요, 아니면 시간이 지나면서 왔다 갔다 했나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 환자 응답] 적어도 몇 주 동안은 계속됐어요. 가라앉은 기분이랑 죄책감, 그리고 멍한 사고가 한 달 정도 저를 계속 짓누르고 있는 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사 질문] 기분이 가라앉거나 정서적으로 저조하지 않을 때도 기억이나 사고에 문제가 생기는 걸 느끼셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 환자 응답] 주로 기분이 가라앉아 있을 때 나타나는 것 같아요. 그럴 때 머리가 멍해지고, 고객 기록에 작은 실수를 하거나 뭘 하려던 건지 잊어버려요. 기분이 괜찮을 때는 그런 일이 똑같이 일어나는 걸 별로 못 느꼈어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사 질문] 요즘 평소보다 죄책감을 느끼거나 스스로를 탓하는 일이 많아지셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 환자 응답] 네. 요즘 스스로를 많이 탓하게 돼요, 특히 저희 삼촌 일로요. 좀 더 자주 전화드리거나 돌아가시기 전에 좀 더 일찍 찾아뵀어야 했는데 하는 생각이 계속 들어요. 머릿속에서 계속 반복 재생되는데, 가족으로서 삼촌한테 못 한 것 같은 느낌이에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사 질문] 예전에 기분이 비교적 괜찮았던 시기에도 기억이나 집중력에 문제가 있었던 걸 느끼신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 환자 응답] 아니요, 딱히 없었어요. 기분이 괜찮았을 때는 이런 멍한 느낌이 있었던 기억이 없어요. 지금 제가 온 이유는 머리가 흐릿한 느낌이 들고, 고객 기록에 작은 실수를 하거나 뭘 하려던 건지 잊어버리는데, 이게 저한테는 정상이 아니라서예요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사 질문] 지금까지 보면 기억이나 집중력 문제가 기분이 가라앉아 있을 때만 나타나나요, 아니면 기분이 괜찮았는데도 그런 문제가 있었던 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 환자 응답] 기분이 가라앉아 있을 때만 그런 것 같아요. 그럴 때 머리가 멍해지고, 고객 기록에 작은 실수를 하기 시작하거나 뭘 하려던 건지 잊어버려요. 기분이 괜찮을 때는 딱히 못 느껴요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사 질문] 즐겨 보던 프로그램을 보거나, 친구들과 시간을 보내거나, 취미 활동을 하는 것처럼 예전에 즐기시던 대부분의 활동에서 즐거움이나 흥미를 못 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 환자 응답] 그렇게까지는 말 못 하겠어요. 가끔은 여전히 뭔가를 즐길 수 있는데, 대부분의 것들에 흥미가 있는지 없는지는 딱히 신경 써서 살펴보진 않았어요. 그보다는... 어떤 날은 그냥 뭘 할 기분이 안 나는 정도예요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사 질문] 예전에 가장 즐기시던 것들을 포함해서 거의 모든 활동에 흥미를 잃으시거나 즐거움을 거의 못 느끼셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 환자 응답] 거의 모든 활동이라고 할 수 있을지는 잘 모르겠어요. 뭘 하고 싶지 않은 시기는 있었지만, 평소에 즐기던 모든 것에 완전히 흥미를 잃었다고는 못 하겠어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사 질문] 적어도 2주 연속으로, 거의 매일 하루의 대부분 동안 기분이 가라앉거나 흥미를 잃은 날들이 있으셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 환자 응답] 네... 요즘 가슴에 무겁고 좀 텅 빈 느낌을 안고 일어나요. 근무는 그럭저럭 버티고 사람들이랑 얘기도 하는데, 속으로는 하루의 많은 시간 동안 그냥 슬프고 멍한 느낌이에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사 질문] 정말 좋아하시던 것들을 포함해서 거의 모든 활동에 흥미를 잃거나 즐거움을 전혀 못 느끼셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 환자 응답] 거의 모든 활동이라고는 못 하겠어요. 가끔 의욕이 줄어든 건 느끼는데, 그래도 여전히 이따금 뭔가에서 즐거움을 느낄 수는 있어요. 모든 게 완전히 무의미하거나 공허하게 느껴지는 건 아니에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
+배경 서술: 구스타보를 키우는 데 큰 도움을 주었던, 시우다드후아레스에 사는 사랑하는 삼촌이 세상을 떠난 뒤, 그는 끊임없이 바쁘게 움직이면 상실감을 억누를 수 있다는 듯이 가족 일 처리, 장례 준비, 차량 수리, 그리고 자신의 간호조무사(CNA) 진로 계획에 몰두했다. 이후 2주 동안 그는 잠을 거의 자지 않아도 괜찮았고, 스페인어 사용 노인 돌봄 기관을 당장 시작할 수 있다는 유난한 자신감을 보였으며, 주의가 산만해져 고객 관련 서류 작업에서 실수를 저지르기도 했지만, 아내와 동료들이 대부분의 문제를 초기에 알아챘다. 그다음 2주 동안 그는 삼촌을 위해 더 많은 것을 하지 못했다는 죄책감과 함께 지속적으로 기분이 가라앉고 피로했으며, 집중력 저하, 불규칙한 수면, 그리고 그를 불안하게 만드는 수동적인 죽음에 대한 생각을 겪었다. 그는 주치의와의 정기 진료 중 이를 언급했고, 주치의는 조울증 양상을 알아채고 그를 이중언어가 가능한 외래 정신건강의학과 전문의에게 의뢰했다.
+표집된 증상 목록:
+  - S024 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.
+  - S027 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.
+  - S029 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.
+  - S030 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).
+  - S031 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.
+  - S032 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.
+  - S033 상승/과민한 기분: 비정상적이고 지속적으로 고양되거나 팽창되거나 과민한 기분이 뚜렷하게 나타나는 기간.
+  - S034 활동 증가: 비정상적이고 지속적으로 증가한 목표지향적 활동이나 에너지.
+  - S035 과장된 자존감: 과장된 자존감이나 과대성(단순한 자신감 과잉부터 망상적 수준까지 다양할 수 있음).
+  - S036 수면 욕구 감소: 수면 욕구가 감소함(예: 단 3시간만 자도 개운함을 느낌).
+  - S039 조증성 산만함: 중요하지 않거나 관련 없는 외부 자극에 지나치게 쉽게 주의가 쏠림.
+  - S040 목표지향 활동 증가: 목표지향적 활동(직장, 학업, 사회, 성적 영역)의 증가 또는 목적 없는 정신운동 초조.</t>
+        </is>
+      </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>[17번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 주요우울장애 (D013, ICD: F32.1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: manic_episode (관계=must_include, 요구개수=5, 충족개수=0, 커버리지=0.0)
-  확인된 근거: (없음)
-  누락: 상승/과민한 기분: 비정상적이고 지속적으로 고양되거나 팽창되거나 과민한 기분이 뚜렷하게 나타나는 기간.; 활동 증가: 비정상적이고 지속적으로 증가한 목표지향적 활동이나 에너지.; 과장된 자존감: 과장된 자존감이나 과대성(단순한 자신감 과잉부터 망상적 수준까지 다양할 수 있음).; 수면 욕구 감소: 수면 욕구가 감소함(예: 단 3시간만 자도 개운함을 느낌).; 압박된 언어: 평소보다 말이 많아지거나 계속 말하려는 압박감을 느낌.; 사고의 질주: 사고의 비약이나 생각이 질주하는 듯한 주관적 경험.; 조증성 산만함: 중요하지 않거나 관련 없는 외부 자극에 지나치게 쉽게 주의가 쏠림.; 목표지향 활동 증가: 목표지향적 활동(직장, 학업, 사회, 성적 영역)의 증가 또는 목적 없는 정신운동 초조.; 위험 결과 초래 행동: 고통스러운 결과를 초래할 가능성이 높은 활동에 지나치게 몰두함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: depressive_episode (관계=include, 요구개수=5, 충족개수=4, 커버리지=0.8)
-  확인된 근거: 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.; 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.; 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).; 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.
-  누락: 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.; 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.; 정신운동 변화: 관찰 가능한 정신운동 활동의 증가 또는 감소.; 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.; 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.</t>
+          <t>의사의 최종 진단: 주요우울장애 (D013, ICD: F32.1)
+지속 기간 요건: None
+기능적 손상 요건: None
+추가 요건: None
+체크리스트 그룹: manic_episode (관계=must_include, 요구개수=5, 충족개수=0, 커버리지=0.0)
+확인된 근거:
+  (없음)
+체크리스트 그룹: depressive_episode (관계=include, 요구개수=5, 충족개수=4, 커버리지=0.8)
+확인된 근거:
+  - 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.
+  - 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.
+  - 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).
+  - 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="A67:B67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D008_S001_P003__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D008_S001_P003__qwen3-235b_kor.xlsx
@@ -922,6 +922,11 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -971,11 +976,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A67:B67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D008_S001_P003__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D008_S001_P003__qwen3-235b_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.0769</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="5">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.0769</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.1806</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
